--- a/output/2026-09-16_18_Croazia_Osječko-baranjska_Cleaning.xlsx
+++ b/output/2026-09-16_18_Croazia_Osječko-baranjska_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro Karcher autorizzato (vendita e service), confermato su karcher.com/hr e sito proprio; 4 e piu moderno centro Karcher in Croazia, area metropolitana di Osijek. Vende aspiratori industriali/professionali e attrezzature per pulizia B2B.</t>
+          <t>Centro Karcher autorizzato (vendita e service), confermato su karcher.com/hr e sito proprio; 4 e piu moderno centro Karcher in Croazia, area metropolitana di Osijek. Vende aspiratori industriali/professionali e attrezzature per pulizia B2B. [DUPLICATO — vedi anche: 2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
